--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring (1).xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\AdvExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C043DE0-3F1C-417A-B08E-4BFB65BF22C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34596574-9E74-4896-8340-5A0D902021EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4717" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4729" uniqueCount="682">
   <si>
     <t>Column1</t>
   </si>
@@ -2053,6 +2053,42 @@
   </si>
   <si>
     <t>SUM OF NORTH ELECTRONICS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>TOTAL ORDERS</t>
+  </si>
+  <si>
+    <t>ORDER BY CASH</t>
+  </si>
+  <si>
+    <t>ORDER BY CARD</t>
+  </si>
+  <si>
+    <t>ORDER BY UPI</t>
+  </si>
+  <si>
+    <t>FIND  NUMBER OF TRANSACTIONS HAVING SALES MORE THAN 4000</t>
+  </si>
+  <si>
+    <t>FIND THE NUMBER OF TRANSACTION THAT ARE MORE THAN 4000 R.</t>
+  </si>
+  <si>
+    <t>EAST</t>
+  </si>
+  <si>
+    <t>NORTH</t>
+  </si>
+  <si>
+    <t>WEST</t>
+  </si>
+  <si>
+    <t>SOUTH</t>
+  </si>
+  <si>
+    <t>COUNT OF SALES FOR CUSTOMER TYPE IS MEMBER AND PAYMENT MODE IS UPI OR CARD</t>
   </si>
 </sst>
 </file>
@@ -2061,7 +2097,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="_ [$₹-4009]\ * #,##0.000_ ;_ [$₹-4009]\ * \-#,##0.000_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.000_ ;_ [$₹-4009]\ * \-#,##0.000_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -2336,7 +2372,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2402,14 +2438,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2423,7 +2451,30 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="60% - Accent1" xfId="3" builtinId="32"/>
@@ -3326,7 +3377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1000"/>
+  <dimension ref="A1:AB1000"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -3353,6 +3404,8 @@
     <col min="22" max="22" width="30.109375" customWidth="1"/>
     <col min="23" max="23" width="7.77734375" customWidth="1"/>
     <col min="24" max="24" width="8.6640625" customWidth="1"/>
+    <col min="25" max="25" width="25" customWidth="1"/>
+    <col min="26" max="26" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3476,7 +3529,6 @@
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -3866,11 +3918,11 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
-      <c r="V8" s="43" t="s">
+      <c r="V8" s="49" t="s">
         <v>667</v>
       </c>
-      <c r="W8" s="1"/>
-      <c r="X8" s="52">
+      <c r="W8" s="48"/>
+      <c r="X8" s="50">
         <f>SUMIFS(dmart_sales_data[sales],dmart_sales_data[Category],"=CLOTHING",dmart_sales_data[updated_region],"=EAST")</f>
         <v>60655.859999999993</v>
       </c>
@@ -3936,11 +3988,11 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
-      <c r="V9" s="43" t="s">
+      <c r="V9" s="49" t="s">
         <v>668</v>
       </c>
-      <c r="W9" s="1"/>
-      <c r="X9" s="52">
+      <c r="W9" s="48"/>
+      <c r="X9" s="50">
         <f>SUMIFS(dmart_sales_data[sales],dmart_sales_data[Category],"GROCERY",dmart_sales_data[updated_region],"EAST")</f>
         <v>52776.310000000012</v>
       </c>
@@ -4006,11 +4058,11 @@
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
-      <c r="V10" s="43" t="s">
+      <c r="V10" s="49" t="s">
         <v>669</v>
       </c>
-      <c r="W10" s="1"/>
-      <c r="X10" s="52">
+      <c r="W10" s="48"/>
+      <c r="X10" s="50">
         <f>SUMIFS(dmart_sales_data[sales],dmart_sales_data[updated_region],"NORTH",dmart_sales_data[Category],"ELECTRONICS",dmart_sales_data[discount],"&gt;0.4")</f>
         <v>36091.269999999997</v>
       </c>
@@ -4073,7 +4125,7 @@
         <v>NO</v>
       </c>
       <c r="R11" s="1"/>
-      <c r="S11" s="43" t="s">
+      <c r="S11" s="49" t="s">
         <v>651</v>
       </c>
       <c r="T11" s="1"/>
@@ -4140,7 +4192,7 @@
         <v>NO</v>
       </c>
       <c r="R12" s="1"/>
-      <c r="S12" s="45">
+      <c r="S12" s="51">
         <f>SUMIF(dmart_sales_data[payment_mode],"UPI",dmart_sales_data[sales])</f>
         <v>386412.25</v>
       </c>
@@ -4208,7 +4260,7 @@
         <v>NO</v>
       </c>
       <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
+      <c r="S13" s="48"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -4273,7 +4325,7 @@
         <v>NO</v>
       </c>
       <c r="R14" s="1"/>
-      <c r="S14" s="43" t="s">
+      <c r="S14" s="49" t="s">
         <v>652</v>
       </c>
       <c r="T14" s="1"/>
@@ -4340,7 +4392,7 @@
         <v>NO</v>
       </c>
       <c r="R15" s="1"/>
-      <c r="S15" s="46">
+      <c r="S15" s="52">
         <f>SUMIF(dmart_sales_data[payment_mode],"=CASH",dmart_sales_data[sales])</f>
         <v>522964.3</v>
       </c>
@@ -4408,7 +4460,7 @@
         <v>NO</v>
       </c>
       <c r="R16" s="1"/>
-      <c r="S16" s="15"/>
+      <c r="S16" s="53"/>
       <c r="T16" s="15"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
@@ -4418,7 +4470,7 @@
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
     </row>
-    <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>51</v>
       </c>
@@ -4473,7 +4525,7 @@
         <v>YES</v>
       </c>
       <c r="R17" s="1"/>
-      <c r="S17" s="15"/>
+      <c r="S17" s="53"/>
       <c r="T17" s="15"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
@@ -4483,7 +4535,7 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>52</v>
       </c>
@@ -4538,19 +4590,24 @@
         <v>YES</v>
       </c>
       <c r="R18" s="1"/>
-      <c r="S18" s="44" t="s">
+      <c r="S18" s="54" t="s">
         <v>653</v>
       </c>
       <c r="T18" s="15"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
+      <c r="U18" s="55"/>
+      <c r="V18" s="55"/>
+      <c r="W18" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="X18" s="1">
+        <f>COUNT(A499)</f>
+        <v>0</v>
+      </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>54</v>
       </c>
@@ -4605,20 +4662,20 @@
         <v>NO</v>
       </c>
       <c r="R19" s="1"/>
-      <c r="S19" s="45">
+      <c r="S19" s="51">
         <f>SUMIF(dmart_sales_data[payment_mode],"=CARD",dmart_sales_data[sales])</f>
         <v>413292.63999999996</v>
       </c>
       <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
+      <c r="U19" s="55"/>
+      <c r="V19" s="55"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>55</v>
       </c>
@@ -4675,15 +4732,15 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
+      <c r="U20" s="55"/>
+      <c r="V20" s="55"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>57</v>
       </c>
@@ -4740,15 +4797,20 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
+      <c r="U21" s="55"/>
+      <c r="V21" s="55"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
+      <c r="Y21" s="48" t="s">
+        <v>671</v>
+      </c>
+      <c r="Z21" s="48">
+        <f>COUNT(dmart_sales_data[quantity])</f>
+        <v>498</v>
+      </c>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>58</v>
       </c>
@@ -4805,15 +4867,20 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
+      <c r="U22" s="55"/>
+      <c r="V22" s="55"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
+      <c r="Y22" s="48" t="s">
+        <v>672</v>
+      </c>
+      <c r="Z22" s="48">
+        <f>COUNTIF(dmart_sales_data[payment_mode],"=CASH")</f>
+        <v>185</v>
+      </c>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>60</v>
       </c>
@@ -4869,16 +4936,20 @@
       </c>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
+      <c r="U23" s="56"/>
+      <c r="V23" s="55"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
+      <c r="Y23" s="48" t="s">
+        <v>673</v>
+      </c>
+      <c r="Z23" s="48">
+        <f>COUNTIF(dmart_sales_data[payment_mode],"=CARD")</f>
+        <v>164</v>
+      </c>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>61</v>
       </c>
@@ -4935,15 +5006,20 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
+      <c r="U24" s="55"/>
+      <c r="V24" s="55"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
+      <c r="Y24" s="48" t="s">
+        <v>674</v>
+      </c>
+      <c r="Z24" s="48">
+        <f>COUNTIF(dmart_sales_data[payment_mode],"=UPI")</f>
+        <v>149</v>
+      </c>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>62</v>
       </c>
@@ -5000,15 +5076,15 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
+      <c r="U25" s="55"/>
+      <c r="V25" s="55"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>63</v>
       </c>
@@ -5073,7 +5149,7 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
@@ -5133,12 +5209,18 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-    </row>
-    <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X27" s="48"/>
+      <c r="Y27" s="60" t="s">
+        <v>675</v>
+      </c>
+      <c r="Z27" s="48">
+        <f>COUNTIF(dmart_sales_data[sales],"&gt;4000")</f>
+        <v>115</v>
+      </c>
+      <c r="AA27" s="58"/>
+      <c r="AB27" s="59"/>
+    </row>
+    <row r="28" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>67</v>
       </c>
@@ -5198,12 +5280,14 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
+      <c r="X28" s="48"/>
+      <c r="Y28" s="60" t="s">
+        <v>676</v>
+      </c>
+      <c r="Z28" s="48"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>68</v>
       </c>
@@ -5263,12 +5347,17 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="61" t="s">
+        <v>678</v>
+      </c>
+      <c r="Z29" s="34">
+        <f>COUNTIFS(dmart_sales_data[sales],"&gt;4000",dmart_sales_data[updated_region],"NORTH")</f>
+        <v>32</v>
+      </c>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>70</v>
       </c>
@@ -5328,12 +5417,17 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
+      <c r="X30" s="48"/>
+      <c r="Y30" s="61" t="s">
+        <v>677</v>
+      </c>
+      <c r="Z30" s="48">
+        <f>COUNTIFS(dmart_sales_data[sales],"&gt;4000",dmart_sales_data[updated_region],"EAST")</f>
+        <v>29</v>
+      </c>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>71</v>
       </c>
@@ -5393,12 +5487,17 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
+      <c r="X31" s="48"/>
+      <c r="Y31" s="61" t="s">
+        <v>679</v>
+      </c>
+      <c r="Z31" s="48">
+        <f>COUNTIFS(dmart_sales_data[sales],"&gt;4000",dmart_sales_data[updated_region],"WEST")</f>
+        <v>27</v>
+      </c>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>72</v>
       </c>
@@ -5458,9 +5557,14 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
+      <c r="X32" s="48"/>
+      <c r="Y32" s="61" t="s">
+        <v>680</v>
+      </c>
+      <c r="Z32" s="48">
+        <f>COUNTIFS(dmart_sales_data[sales],"&gt;4000",dmart_sales_data[updated_region],"SOUTH")</f>
+        <v>27</v>
+      </c>
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -5589,8 +5693,13 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
+      <c r="Y34" s="57" t="s">
+        <v>681</v>
+      </c>
+      <c r="Z34" s="1">
+        <f>COUNTIFS(dmart_sales_data[customer_type],"MEMBER",dmart_sales_data[payment_mode],"UPI")+COUNTIFS(dmart_sales_data[customer_type],"MEMBER",dmart_sales_data[payment_mode],"CARD")</f>
+        <v>97</v>
+      </c>
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -50277,27 +50386,27 @@
   </cols>
   <sheetData>
     <row r="6" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="43" t="s">
         <v>654</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="43" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="45" t="s">
         <v>655</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="45" t="s">
         <v>656</v>
       </c>
-      <c r="D7" s="50">
+      <c r="D7" s="46">
         <v>2300</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="44" t="s">
         <v>663</v>
       </c>
       <c r="G7" s="34">
@@ -50306,16 +50415,16 @@
       </c>
     </row>
     <row r="8" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="45" t="s">
         <v>655</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="45" t="s">
         <v>657</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="46">
         <v>5500</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F8" s="47" t="s">
         <v>664</v>
       </c>
       <c r="G8" s="34">
@@ -50324,14 +50433,14 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B9" s="49"/>
-      <c r="C9" s="49" t="s">
+      <c r="B9" s="45"/>
+      <c r="C9" s="45" t="s">
         <v>665</v>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="46">
         <v>30</v>
       </c>
-      <c r="F9" s="51" t="s">
+      <c r="F9" s="47" t="s">
         <v>666</v>
       </c>
       <c r="G9" s="34">
@@ -50340,44 +50449,44 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="45" t="s">
         <v>658</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="45" t="s">
         <v>659</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="46">
         <v>800</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B11" s="49"/>
-      <c r="C11" s="49" t="s">
+      <c r="B11" s="45"/>
+      <c r="C11" s="45" t="s">
         <v>660</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="46">
         <v>400</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="45" t="s">
         <v>655</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="45" t="s">
         <v>661</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="46">
         <v>4200</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="45" t="s">
         <v>658</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="45" t="s">
         <v>662</v>
       </c>
-      <c r="D13" s="50">
+      <c r="D13" s="46">
         <v>1200</v>
       </c>
     </row>

--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring (1).xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring (1).xlsx
@@ -8,20 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\AdvExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34596574-9E74-4896-8340-5A0D902021EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B46F06-A931-4162-B1E0-A4CB5898DEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="database" sheetId="1" r:id="rId1"/>
     <sheet name="falshfill" sheetId="3" r:id="rId2"/>
     <sheet name="custmlist" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
-    <sheet name="Sheet1 (2)" sheetId="8" r:id="rId5"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId7"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId8"/>
+    <sheet name="subtotal" sheetId="10" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet1 (2)" sheetId="8" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">subtotal!$A$2:$A$9</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,14 +40,36 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4729" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4778" uniqueCount="697">
   <si>
     <t>Column1</t>
   </si>
@@ -2089,21 +2115,74 @@
   </si>
   <si>
     <t>COUNT OF SALES FOR CUSTOMER TYPE IS MEMBER AND PAYMENT MODE IS UPI OR CARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> total sales by north </t>
+  </si>
+  <si>
+    <t>total sales by south</t>
+  </si>
+  <si>
+    <t>total sales by east</t>
+  </si>
+  <si>
+    <t>total sales by west</t>
+  </si>
+  <si>
+    <t>number of orders by :</t>
+  </si>
+  <si>
+    <t>north</t>
+  </si>
+  <si>
+    <t>south</t>
+  </si>
+  <si>
+    <t>west</t>
+  </si>
+  <si>
+    <t>east</t>
+  </si>
+  <si>
+    <t>orders</t>
+  </si>
+  <si>
+    <t>sales for 2023</t>
+  </si>
+  <si>
+    <t>sales for2024</t>
+  </si>
+  <si>
+    <t>last 6 month sales 2023</t>
+  </si>
+  <si>
+    <t>last 6 month sales 2024</t>
+  </si>
+  <si>
+    <t>Data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.000_ ;_ [$₹-4009]\ * \-#,##0.000_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2215,8 +2294,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12.3"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2259,8 +2344,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -2365,124 +2462,242 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFA4A4A4"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFA4A4A4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="3" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="4"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="40% - Accent2" xfId="4" builtinId="35"/>
     <cellStyle name="60% - Accent1" xfId="3" builtinId="32"/>
     <cellStyle name="60% - Accent2" xfId="2" builtinId="36"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="56">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2622,6 +2837,576 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2986,33 +3771,6 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
@@ -3150,32 +3908,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3603E45-D150-45C5-8256-7215A06F2288}" name="dmart_sales_data" displayName="dmart_sales_data" ref="A1:Q499" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32" tableBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3603E45-D150-45C5-8256-7215A06F2288}" name="dmart_sales_data" displayName="dmart_sales_data" ref="A1:Q500" totalsRowCount="1" headerRowDxfId="55" dataDxfId="54" tableBorderDxfId="53">
   <autoFilter ref="A1:Q499" xr:uid="{D3603E45-D150-45C5-8256-7215A06F2288}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{476BF0BA-B9F3-49AC-BB5A-2D10A153742A}" name="Column1" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{A63F91C7-46BC-4000-BB35-6C4A8D2065F6}" name="Region" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{253A47F9-A5A1-44F7-86E3-0DF339744670}" name="updated_region" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{4472310D-0660-4CA1-A746-E4787DA4E6EB}" name="Category" dataDxfId="27"/>
-    <tableColumn id="14" xr3:uid="{90ACAA4C-9C63-491E-BF3F-7C8AD00A0973}" name="SALES_RANGE" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{476BF0BA-B9F3-49AC-BB5A-2D10A153742A}" name="Column1" dataDxfId="52" totalsRowDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{A63F91C7-46BC-4000-BB35-6C4A8D2065F6}" name="Region" dataDxfId="51" totalsRowDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{253A47F9-A5A1-44F7-86E3-0DF339744670}" name="updated_region" dataDxfId="50" totalsRowDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{4472310D-0660-4CA1-A746-E4787DA4E6EB}" name="Category" dataDxfId="49" totalsRowDxfId="27"/>
+    <tableColumn id="14" xr3:uid="{90ACAA4C-9C63-491E-BF3F-7C8AD00A0973}" name="SALES_RANGE" dataDxfId="48" totalsRowDxfId="26">
       <calculatedColumnFormula>IF(dmart_sales_data[[#This Row],[sales]]&lt;1000,"LOW_SALES",IF(F2&lt;3000,"MEDIAN_SALES","HIGH_SALES"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{59FFB5BE-8268-4CF1-A5FA-406580A1FD1D}" name="sales" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{10694E4C-EFF1-4641-85C6-44F9CBC8E6D6}" name="discount" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{2DC5A30C-390E-4DC1-9CC5-BA0758B8B931}" name="quantity" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{20D7019E-213C-4E8C-9984-D5F6A541588F}" name="order_date" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{4B10BFCC-E07E-42B7-8090-4AC57A685125}" name="delivery_date" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{77D21F91-ACE4-4D89-A896-4421C009D6EE}" name="customer_type" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{D931A1BC-F066-4CCE-A2A2-450BD451AC4F}" name="customer_type2" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{EF8D940B-7D82-4A73-867F-F14216B509E8}" name="payment_mode" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{9BBBCC3B-E910-4C46-8A47-E6CD67374B7F}" name="profit" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{048CF9AB-9C7A-46BA-A7E3-B7B197A782F3}" name="update_city" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{234FD248-A670-48A9-9572-852F524A8B48}" name="city" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{928221A7-E12E-4777-BF9E-D03D772639FF}" name="DISCOUNT2" dataDxfId="14">
+    <tableColumn id="4" xr3:uid="{59FFB5BE-8268-4CF1-A5FA-406580A1FD1D}" name="sales" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{10694E4C-EFF1-4641-85C6-44F9CBC8E6D6}" name="discount" dataDxfId="47" totalsRowDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{2DC5A30C-390E-4DC1-9CC5-BA0758B8B931}" name="quantity" dataDxfId="46" totalsRowDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{20D7019E-213C-4E8C-9984-D5F6A541588F}" name="order_date" dataDxfId="45" totalsRowDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{4B10BFCC-E07E-42B7-8090-4AC57A685125}" name="delivery_date" dataDxfId="44" totalsRowDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{77D21F91-ACE4-4D89-A896-4421C009D6EE}" name="customer_type" dataDxfId="43" totalsRowDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{D931A1BC-F066-4CCE-A2A2-450BD451AC4F}" name="customer_type2" dataDxfId="42" totalsRowDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{EF8D940B-7D82-4A73-867F-F14216B509E8}" name="payment_mode" dataDxfId="41" totalsRowDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{9BBBCC3B-E910-4C46-8A47-E6CD67374B7F}" name="profit" dataDxfId="40" totalsRowDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{048CF9AB-9C7A-46BA-A7E3-B7B197A782F3}" name="update_city" dataDxfId="39" totalsRowDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{234FD248-A670-48A9-9572-852F524A8B48}" name="city" dataDxfId="38" totalsRowDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{928221A7-E12E-4777-BF9E-D03D772639FF}" name="DISCOUNT2" dataDxfId="37" totalsRowDxfId="15">
       <calculatedColumnFormula>IF(AND(dmart_sales_data[[#This Row],[customer_type2]]="MEMBER",OR(dmart_sales_data[[#This Row],[payment_mode]]="UPI",dmart_sales_data[[#This Row],[payment_mode]]="CARD")),"YES","NO")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{59722358-51FC-47C5-BE58-6079BEEAA5D7}" name="Table2" displayName="Table2" ref="S33:T37" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="35" tableBorderDxfId="36" totalsRowBorderDxfId="34">
+  <autoFilter ref="S33:T37" xr:uid="{59722358-51FC-47C5-BE58-6079BEEAA5D7}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{106C2011-3EF6-4B2A-81EE-A1C34F5A35B7}" name="number of orders by :" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{D424500C-273D-4584-9E54-AB032F3C62E6}" name="orders" dataDxfId="32"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3377,7 +4146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:AA1000"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -4470,7 +5239,7 @@
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
     </row>
-    <row r="17" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>51</v>
       </c>
@@ -4535,7 +5304,7 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>52</v>
       </c>
@@ -4594,8 +5363,8 @@
         <v>653</v>
       </c>
       <c r="T18" s="15"/>
-      <c r="U18" s="55"/>
-      <c r="V18" s="55"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
       <c r="W18" s="1" t="s">
         <v>670</v>
       </c>
@@ -4607,7 +5376,7 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>54</v>
       </c>
@@ -4667,15 +5436,15 @@
         <v>413292.63999999996</v>
       </c>
       <c r="T19" s="1"/>
-      <c r="U19" s="55"/>
-      <c r="V19" s="55"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>55</v>
       </c>
@@ -4732,15 +5501,15 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="55"/>
-      <c r="V20" s="55"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>57</v>
       </c>
@@ -4797,8 +5566,8 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
-      <c r="U21" s="55"/>
-      <c r="V21" s="55"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="48" t="s">
@@ -4810,7 +5579,7 @@
       </c>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>58</v>
       </c>
@@ -4867,8 +5636,8 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
-      <c r="U22" s="55"/>
-      <c r="V22" s="55"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="48" t="s">
@@ -4880,7 +5649,7 @@
       </c>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>60</v>
       </c>
@@ -4935,9 +5704,10 @@
         <v>NO</v>
       </c>
       <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="U23" s="56"/>
-      <c r="V23" s="55"/>
+      <c r="S23" s="48" t="s">
+        <v>682</v>
+      </c>
+      <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="48" t="s">
@@ -4949,7 +5719,7 @@
       </c>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>61</v>
       </c>
@@ -5004,10 +5774,13 @@
         <v>NO</v>
       </c>
       <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
+      <c r="S24" s="57">
+        <f>SUMIF(dmart_sales_data[updated_region],"north",dmart_sales_data[sales])</f>
+        <v>334964.16000000003</v>
+      </c>
       <c r="T24" s="1"/>
-      <c r="U24" s="55"/>
-      <c r="V24" s="55"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="48" t="s">
@@ -5019,7 +5792,7 @@
       </c>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>62</v>
       </c>
@@ -5074,17 +5847,19 @@
         <v>NO</v>
       </c>
       <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
+      <c r="S25" s="48" t="s">
+        <v>683</v>
+      </c>
       <c r="T25" s="1"/>
-      <c r="U25" s="55"/>
-      <c r="V25" s="55"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>63</v>
       </c>
@@ -5139,7 +5914,10 @@
         <v>NO</v>
       </c>
       <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
+      <c r="S26" s="57">
+        <f>SUMIF(dmart_sales_data[updated_region],"south",dmart_sales_data[sales])</f>
+        <v>303623.68999999994</v>
+      </c>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
@@ -5149,7 +5927,7 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>65</v>
       </c>
@@ -5204,23 +5982,24 @@
         <v>NO</v>
       </c>
       <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
+      <c r="S27" s="48" t="s">
+        <v>684</v>
+      </c>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="48"/>
-      <c r="Y27" s="60" t="s">
+      <c r="Y27" s="56" t="s">
         <v>675</v>
       </c>
       <c r="Z27" s="48">
         <f>COUNTIF(dmart_sales_data[sales],"&gt;4000")</f>
         <v>115</v>
       </c>
-      <c r="AA27" s="58"/>
-      <c r="AB27" s="59"/>
-    </row>
-    <row r="28" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA27" s="1"/>
+    </row>
+    <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>67</v>
       </c>
@@ -5275,19 +6054,22 @@
         <v>YES</v>
       </c>
       <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
+      <c r="S28" s="57">
+        <f>SUMIF(dmart_sales_data[updated_region],"east",dmart_sales_data[sales])</f>
+        <v>337881.26999999996</v>
+      </c>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="48"/>
-      <c r="Y28" s="60" t="s">
+      <c r="Y28" s="56" t="s">
         <v>676</v>
       </c>
       <c r="Z28" s="48"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>68</v>
       </c>
@@ -5342,13 +6124,15 @@
         <v>NO</v>
       </c>
       <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
+      <c r="S29" s="48" t="s">
+        <v>685</v>
+      </c>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="48"/>
-      <c r="Y29" s="61" t="s">
+      <c r="Y29" s="48" t="s">
         <v>678</v>
       </c>
       <c r="Z29" s="34">
@@ -5357,7 +6141,7 @@
       </c>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>70</v>
       </c>
@@ -5412,13 +6196,16 @@
         <v>YES</v>
       </c>
       <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
+      <c r="S30" s="57">
+        <f>SUMIF(dmart_sales_data[updated_region],"west",dmart_sales_data[sales])</f>
+        <v>346200.06999999983</v>
+      </c>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="48"/>
-      <c r="Y30" s="61" t="s">
+      <c r="Y30" s="48" t="s">
         <v>677</v>
       </c>
       <c r="Z30" s="48">
@@ -5427,7 +6214,7 @@
       </c>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>71</v>
       </c>
@@ -5488,7 +6275,7 @@
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="48"/>
-      <c r="Y31" s="61" t="s">
+      <c r="Y31" s="48" t="s">
         <v>679</v>
       </c>
       <c r="Z31" s="48">
@@ -5497,7 +6284,7 @@
       </c>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>72</v>
       </c>
@@ -5558,7 +6345,7 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="48"/>
-      <c r="Y32" s="61" t="s">
+      <c r="Y32" s="48" t="s">
         <v>680</v>
       </c>
       <c r="Z32" s="48">
@@ -5622,8 +6409,12 @@
         <v>NO</v>
       </c>
       <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
+      <c r="S33" s="60" t="s">
+        <v>686</v>
+      </c>
+      <c r="T33" s="61" t="s">
+        <v>691</v>
+      </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
@@ -5687,13 +6478,18 @@
         <v>NO</v>
       </c>
       <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
+      <c r="S34" s="58" t="s">
+        <v>687</v>
+      </c>
+      <c r="T34" s="59">
+        <f>COUNTIF(dmart_sales_data[updated_region],"north")</f>
+        <v>124</v>
+      </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-      <c r="Y34" s="57" t="s">
+      <c r="Y34" s="55" t="s">
         <v>681</v>
       </c>
       <c r="Z34" s="1">
@@ -5757,8 +6553,13 @@
         <v>NO</v>
       </c>
       <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
+      <c r="S35" s="58" t="s">
+        <v>688</v>
+      </c>
+      <c r="T35" s="59">
+        <f>COUNTIF(dmart_sales_data[updated_region],"south")</f>
+        <v>124</v>
+      </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
@@ -5822,8 +6623,13 @@
         <v>NO</v>
       </c>
       <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
+      <c r="S36" s="58" t="s">
+        <v>689</v>
+      </c>
+      <c r="T36" s="59">
+        <f>COUNTIF(dmart_sales_data[updated_region],"west")</f>
+        <v>125</v>
+      </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
@@ -5887,8 +6693,13 @@
         <v>NO</v>
       </c>
       <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
+      <c r="S37" s="62" t="s">
+        <v>690</v>
+      </c>
+      <c r="T37" s="63">
+        <f>COUNTIF(dmart_sales_data[updated_region],"east")</f>
+        <v>125</v>
+      </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
@@ -6147,8 +6958,13 @@
         <v>YES</v>
       </c>
       <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
+      <c r="S41" s="64" t="s">
+        <v>692</v>
+      </c>
+      <c r="T41" s="64">
+        <f>SUMIFS(dmart_sales_data[sales],dmart_sales_data[order_date],"&gt;1-1-2023",dmart_sales_data[order_date],"&lt;31-12-2023")</f>
+        <v>654586.69000000018</v>
+      </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
@@ -6212,10 +7028,18 @@
         <v>NO</v>
       </c>
       <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
+      <c r="S42" s="64" t="s">
+        <v>693</v>
+      </c>
+      <c r="T42" s="64">
+        <f>SUMIFS(dmart_sales_data[sales],dmart_sales_data[order_date],"&gt;1-1-2024",dmart_sales_data[order_date],"&lt;31-12-2024")</f>
+        <v>660890.80000000016</v>
+      </c>
       <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
+      <c r="V42" s="65">
+        <f xml:space="preserve"> MAX(dmart_sales_data[order_date])</f>
+        <v>45657</v>
+      </c>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
@@ -6277,10 +7101,18 @@
         <v>YES</v>
       </c>
       <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
+      <c r="S43" s="64" t="s">
+        <v>694</v>
+      </c>
+      <c r="T43" s="64">
+        <f>SUMIFS(dmart_sales_data[sales],dmart_sales_data[order_date],"&gt;=1-7-2023",dmart_sales_data[order_date],"&lt;=31-12-2023")</f>
+        <v>348993.08999999991</v>
+      </c>
       <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
+      <c r="V43" s="65">
+        <f>MIN(dmart_sales_data[order_date])</f>
+        <v>44932</v>
+      </c>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -6342,8 +7174,13 @@
         <v>NO</v>
       </c>
       <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
+      <c r="S44" s="64" t="s">
+        <v>695</v>
+      </c>
+      <c r="T44" s="64">
+        <f>SUMIFS(dmart_sales_data[sales],dmart_sales_data[order_date],"&gt;=1-7-2024",dmart_sales_data[order_date],"&lt;=31-12-2024")</f>
+        <v>368049.34999999992</v>
+      </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
@@ -6407,8 +7244,6 @@
         <v>NO</v>
       </c>
       <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
@@ -6540,7 +7375,7 @@
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
+      <c r="V47" s="68"/>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -35928,23 +36763,22 @@
       <c r="AA499" s="1"/>
     </row>
     <row r="500" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="1"/>
-      <c r="B500" s="2"/>
-      <c r="C500" s="1"/>
-      <c r="D500" s="1"/>
-      <c r="E500" s="1"/>
-      <c r="F500" s="1"/>
-      <c r="G500" s="1"/>
-      <c r="H500" s="1"/>
-      <c r="I500" s="1"/>
-      <c r="J500" s="1"/>
-      <c r="K500" s="1"/>
-      <c r="L500" s="1"/>
-      <c r="M500" s="1"/>
-      <c r="N500" s="1"/>
-      <c r="O500" s="1"/>
-      <c r="P500" s="1"/>
-      <c r="Q500" s="1"/>
+      <c r="A500" s="66"/>
+      <c r="B500" s="32"/>
+      <c r="C500" s="32"/>
+      <c r="D500" s="24"/>
+      <c r="E500" s="24"/>
+      <c r="G500" s="24"/>
+      <c r="H500" s="24"/>
+      <c r="I500" s="67"/>
+      <c r="J500" s="67"/>
+      <c r="K500" s="24"/>
+      <c r="L500" s="24"/>
+      <c r="M500" s="24"/>
+      <c r="N500" s="24"/>
+      <c r="O500" s="24"/>
+      <c r="P500" s="21"/>
+      <c r="Q500" s="24"/>
       <c r="R500" s="1"/>
       <c r="S500" s="1"/>
       <c r="T500" s="1"/>
@@ -48954,8 +49788,8 @@
       <c r="X1000" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="F1:F1048576">
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="F1:F499 F501:F1048576 V47">
     <cfRule type="top10" dxfId="13" priority="7" bottom="1" rank="10"/>
     <cfRule type="top10" dxfId="12" priority="8" rank="10"/>
     <cfRule type="top10" dxfId="11" priority="9" rank="10"/>
@@ -48996,8 +49830,9 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -49126,7 +49961,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD2C2FD5-8379-4925-B2E3-1BBDDF1E9A2D}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -49135,12 +49970,6 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>577</v>
-      </c>
-      <c r="B1" t="s">
-        <v>582</v>
-      </c>
       <c r="C1" t="s">
         <v>590</v>
       </c>
@@ -49173,12 +50002,6 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>578</v>
-      </c>
-      <c r="B2" t="s">
-        <v>583</v>
-      </c>
       <c r="C2" t="s">
         <v>583</v>
       </c>
@@ -49210,12 +50033,6 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>579</v>
-      </c>
-      <c r="B3" t="s">
-        <v>584</v>
-      </c>
       <c r="C3" t="s">
         <v>584</v>
       </c>
@@ -49247,12 +50064,6 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>580</v>
-      </c>
-      <c r="B4" t="s">
-        <v>585</v>
-      </c>
       <c r="C4" t="s">
         <v>585</v>
       </c>
@@ -49284,12 +50095,6 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>581</v>
-      </c>
-      <c r="B5" t="s">
-        <v>586</v>
-      </c>
       <c r="C5" t="s">
         <v>586</v>
       </c>
@@ -49321,12 +50126,6 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>578</v>
-      </c>
-      <c r="B6" t="s">
-        <v>587</v>
-      </c>
       <c r="C6" t="s">
         <v>587</v>
       </c>
@@ -49342,12 +50141,6 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>579</v>
-      </c>
-      <c r="B7" t="s">
-        <v>588</v>
-      </c>
       <c r="C7" t="s">
         <v>588</v>
       </c>
@@ -49369,12 +50162,6 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>580</v>
-      </c>
-      <c r="B8" t="s">
-        <v>589</v>
-      </c>
       <c r="C8" t="s">
         <v>589</v>
       </c>
@@ -49593,32 +50380,301 @@
       <c r="A18" t="s">
         <v>578</v>
       </c>
+      <c r="I18" t="s">
+        <v>577</v>
+      </c>
+      <c r="J18" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>579</v>
       </c>
+      <c r="I19" t="s">
+        <v>578</v>
+      </c>
+      <c r="J19" t="s">
+        <v>583</v>
+      </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>580</v>
       </c>
+      <c r="I20" t="s">
+        <v>579</v>
+      </c>
+      <c r="J20" t="s">
+        <v>584</v>
+      </c>
+      <c r="L20" cm="1">
+        <f t="array" ref="L20:L43">COUNTIF(J19:J42,J19:J42)</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>581</v>
       </c>
+      <c r="I21" t="s">
+        <v>580</v>
+      </c>
+      <c r="J21" t="s">
+        <v>585</v>
+      </c>
+      <c r="L21">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>578</v>
+      </c>
+      <c r="I22" t="s">
+        <v>581</v>
+      </c>
+      <c r="J22" t="s">
+        <v>586</v>
+      </c>
+      <c r="L22">
+        <v>6</v>
+      </c>
+      <c r="N22">
+        <f>COUNTIF(J19:J42,J19)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I23" t="s">
+        <v>578</v>
+      </c>
+      <c r="J23" t="s">
+        <v>583</v>
+      </c>
+      <c r="L23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I24" t="s">
+        <v>579</v>
+      </c>
+      <c r="J24" t="s">
+        <v>584</v>
+      </c>
+      <c r="L24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I25" t="s">
+        <v>580</v>
+      </c>
+      <c r="J25" t="s">
+        <v>585</v>
+      </c>
+      <c r="L25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I26" t="s">
+        <v>581</v>
+      </c>
+      <c r="J26" t="s">
+        <v>586</v>
+      </c>
+      <c r="L26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I27" t="s">
+        <v>578</v>
+      </c>
+      <c r="J27" t="s">
+        <v>583</v>
+      </c>
+      <c r="L27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I28" t="s">
+        <v>579</v>
+      </c>
+      <c r="J28" t="s">
+        <v>584</v>
+      </c>
+      <c r="L28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I29" t="s">
+        <v>580</v>
+      </c>
+      <c r="J29" t="s">
+        <v>585</v>
+      </c>
+      <c r="L29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I30" t="s">
+        <v>581</v>
+      </c>
+      <c r="J30" t="s">
+        <v>586</v>
+      </c>
+      <c r="L30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I31" t="s">
+        <v>578</v>
+      </c>
+      <c r="J31" t="s">
+        <v>583</v>
+      </c>
+      <c r="L31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I32" t="s">
+        <v>579</v>
+      </c>
+      <c r="J32" t="s">
+        <v>584</v>
+      </c>
+      <c r="L32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I33" t="s">
+        <v>580</v>
+      </c>
+      <c r="J33" t="s">
+        <v>585</v>
+      </c>
+      <c r="L33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I34" t="s">
+        <v>581</v>
+      </c>
+      <c r="J34" t="s">
+        <v>586</v>
+      </c>
+      <c r="L34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I35" t="s">
+        <v>578</v>
+      </c>
+      <c r="J35" t="s">
+        <v>583</v>
+      </c>
+      <c r="L35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I36" t="s">
+        <v>579</v>
+      </c>
+      <c r="J36" t="s">
+        <v>584</v>
+      </c>
+      <c r="L36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I37" t="s">
+        <v>580</v>
+      </c>
+      <c r="J37" t="s">
+        <v>585</v>
+      </c>
+      <c r="L37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I38" t="s">
+        <v>581</v>
+      </c>
+      <c r="J38" t="s">
+        <v>586</v>
+      </c>
+      <c r="L38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I39" t="s">
+        <v>578</v>
+      </c>
+      <c r="J39" t="s">
+        <v>583</v>
+      </c>
+      <c r="L39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I40" t="s">
+        <v>579</v>
+      </c>
+      <c r="J40" t="s">
+        <v>584</v>
+      </c>
+      <c r="L40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I41" t="s">
+        <v>580</v>
+      </c>
+      <c r="J41" t="s">
+        <v>585</v>
+      </c>
+      <c r="L41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I42" t="s">
+        <v>581</v>
+      </c>
+      <c r="J42" t="s">
+        <v>586</v>
+      </c>
+      <c r="L42">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="L43">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E2:F11">
     <sortCondition ref="E2:E11" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F1:F1048576">
     <cfRule type="dataBar" priority="5">
       <dataBar>
@@ -49703,6 +50759,90 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93001591-1A6E-4569-BF7A-F8CB04F550E8}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A2:D12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="72" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="73">
+        <v>230</v>
+      </c>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="71">
+        <v>150</v>
+      </c>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+    </row>
+    <row r="5" spans="1:4" ht="15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="71">
+        <v>120</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+    </row>
+    <row r="6" spans="1:4" ht="15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="71">
+        <v>45</v>
+      </c>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="71">
+        <v>23</v>
+      </c>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C9">
+        <f>SUBTOTAL(9,A3:A8)</f>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C10">
+        <f>SUBTOTAL(1,A3:A8)</f>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C12">
+        <f>SUBTOTAL(109,A3:A4)</f>
+        <v>380</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:A9" xr:uid="{93001591-1A6E-4569-BF7A-F8CB04F550E8}">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="greaterThanOrEqual" val="150"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A9">
+    <sortCondition descending="1" ref="A2:A9"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590F0D32-DBB8-4CC9-8A57-171EDF175381}">
   <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -49773,12 +50913,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F02A7BE-E1C5-4681-8B4B-C0C08429C705}">
   <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -49849,12 +50989,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28C9A9AD-5F32-4857-99F9-E62FFABCCDFF}">
   <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -49925,12 +51065,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9ADD8E7-B498-4D82-A60B-0B043A12DAA9}">
   <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -50368,12 +51508,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4104CA52-2D7F-4EF7-993E-1FA74469FB6C}">
   <dimension ref="B6:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring (1).xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring (1).xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\AdvExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B46F06-A931-4162-B1E0-A4CB5898DEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1E95C1-ABA9-45A5-A8EA-DCF4D884C4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="database" sheetId="1" r:id="rId1"/>
     <sheet name="falshfill" sheetId="3" r:id="rId2"/>
     <sheet name="custmlist" sheetId="4" r:id="rId3"/>
     <sheet name="subtotal" sheetId="10" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
+    <sheet name="counts" sheetId="6" r:id="rId5"/>
     <sheet name="Sheet1 (2)" sheetId="8" r:id="rId6"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId8"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4778" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4775" uniqueCount="701">
   <si>
     <t>Column1</t>
   </si>
@@ -2160,6 +2160,18 @@
   </si>
   <si>
     <t>Data</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>count blanck</t>
+  </si>
+  <si>
+    <t>counta</t>
+  </si>
+  <si>
+    <t>hii</t>
   </si>
 </sst>
 </file>
@@ -2171,11 +2183,18 @@
     <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.000_ ;_ [$₹-4009]\ * \-#,##0.000_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2301,7 +2320,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2354,6 +2373,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -2559,138 +2584,141 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="3" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="4"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="4"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="5"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
+    <cellStyle name="20% - Accent2" xfId="5" builtinId="34"/>
     <cellStyle name="40% - Accent2" xfId="4" builtinId="35"/>
     <cellStyle name="60% - Accent1" xfId="3" builtinId="32"/>
     <cellStyle name="60% - Accent2" xfId="2" builtinId="36"/>
@@ -2849,6 +2877,153 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
@@ -2876,7 +3051,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -2884,7 +3059,9 @@
       </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
-        <right/>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
         <top style="thin">
           <color theme="1"/>
         </top>
@@ -2959,7 +3136,59 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -3011,417 +3240,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3446,7 +3264,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -3454,9 +3272,7 @@
       </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
+        <right/>
         <top style="thin">
           <color theme="1"/>
         </top>
@@ -3504,6 +3320,223 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -3583,73 +3616,16 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
           <color theme="1"/>
         </top>
         <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3693,44 +3669,16 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
           <color theme="1"/>
         </top>
         <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3774,6 +3722,32 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3801,6 +3775,32 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3812,6 +3812,34 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3911,25 +3939,25 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3603E45-D150-45C5-8256-7215A06F2288}" name="dmart_sales_data" displayName="dmart_sales_data" ref="A1:Q500" totalsRowCount="1" headerRowDxfId="55" dataDxfId="54" tableBorderDxfId="53">
   <autoFilter ref="A1:Q499" xr:uid="{D3603E45-D150-45C5-8256-7215A06F2288}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{476BF0BA-B9F3-49AC-BB5A-2D10A153742A}" name="Column1" dataDxfId="52" totalsRowDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{A63F91C7-46BC-4000-BB35-6C4A8D2065F6}" name="Region" dataDxfId="51" totalsRowDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{253A47F9-A5A1-44F7-86E3-0DF339744670}" name="updated_region" dataDxfId="50" totalsRowDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{4472310D-0660-4CA1-A746-E4787DA4E6EB}" name="Category" dataDxfId="49" totalsRowDxfId="27"/>
-    <tableColumn id="14" xr3:uid="{90ACAA4C-9C63-491E-BF3F-7C8AD00A0973}" name="SALES_RANGE" dataDxfId="48" totalsRowDxfId="26">
+    <tableColumn id="1" xr3:uid="{476BF0BA-B9F3-49AC-BB5A-2D10A153742A}" name="Column1" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{A63F91C7-46BC-4000-BB35-6C4A8D2065F6}" name="Region" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="16" xr3:uid="{253A47F9-A5A1-44F7-86E3-0DF339744670}" name="updated_region" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{4472310D-0660-4CA1-A746-E4787DA4E6EB}" name="Category" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="14" xr3:uid="{90ACAA4C-9C63-491E-BF3F-7C8AD00A0973}" name="SALES_RANGE" dataDxfId="44" totalsRowDxfId="43">
       <calculatedColumnFormula>IF(dmart_sales_data[[#This Row],[sales]]&lt;1000,"LOW_SALES",IF(F2&lt;3000,"MEDIAN_SALES","HIGH_SALES"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{59FFB5BE-8268-4CF1-A5FA-406580A1FD1D}" name="sales" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{10694E4C-EFF1-4641-85C6-44F9CBC8E6D6}" name="discount" dataDxfId="47" totalsRowDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{2DC5A30C-390E-4DC1-9CC5-BA0758B8B931}" name="quantity" dataDxfId="46" totalsRowDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{20D7019E-213C-4E8C-9984-D5F6A541588F}" name="order_date" dataDxfId="45" totalsRowDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{4B10BFCC-E07E-42B7-8090-4AC57A685125}" name="delivery_date" dataDxfId="44" totalsRowDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{77D21F91-ACE4-4D89-A896-4421C009D6EE}" name="customer_type" dataDxfId="43" totalsRowDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{D931A1BC-F066-4CCE-A2A2-450BD451AC4F}" name="customer_type2" dataDxfId="42" totalsRowDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{EF8D940B-7D82-4A73-867F-F14216B509E8}" name="payment_mode" dataDxfId="41" totalsRowDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{9BBBCC3B-E910-4C46-8A47-E6CD67374B7F}" name="profit" dataDxfId="40" totalsRowDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{048CF9AB-9C7A-46BA-A7E3-B7B197A782F3}" name="update_city" dataDxfId="39" totalsRowDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{234FD248-A670-48A9-9572-852F524A8B48}" name="city" dataDxfId="38" totalsRowDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{928221A7-E12E-4777-BF9E-D03D772639FF}" name="DISCOUNT2" dataDxfId="37" totalsRowDxfId="15">
+    <tableColumn id="4" xr3:uid="{59FFB5BE-8268-4CF1-A5FA-406580A1FD1D}" name="sales" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{10694E4C-EFF1-4641-85C6-44F9CBC8E6D6}" name="discount" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{2DC5A30C-390E-4DC1-9CC5-BA0758B8B931}" name="quantity" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{20D7019E-213C-4E8C-9984-D5F6A541588F}" name="order_date" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{4B10BFCC-E07E-42B7-8090-4AC57A685125}" name="delivery_date" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{77D21F91-ACE4-4D89-A896-4421C009D6EE}" name="customer_type" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{D931A1BC-F066-4CCE-A2A2-450BD451AC4F}" name="customer_type2" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{EF8D940B-7D82-4A73-867F-F14216B509E8}" name="payment_mode" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="12" xr3:uid="{9BBBCC3B-E910-4C46-8A47-E6CD67374B7F}" name="profit" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="15" xr3:uid="{048CF9AB-9C7A-46BA-A7E3-B7B197A782F3}" name="update_city" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{234FD248-A670-48A9-9572-852F524A8B48}" name="city" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{928221A7-E12E-4777-BF9E-D03D772639FF}" name="DISCOUNT2" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>IF(AND(dmart_sales_data[[#This Row],[customer_type2]]="MEMBER",OR(dmart_sales_data[[#This Row],[payment_mode]]="UPI",dmart_sales_data[[#This Row],[payment_mode]]="CARD")),"YES","NO")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3938,11 +3966,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{59722358-51FC-47C5-BE58-6079BEEAA5D7}" name="Table2" displayName="Table2" ref="S33:T37" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="35" tableBorderDxfId="36" totalsRowBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{59722358-51FC-47C5-BE58-6079BEEAA5D7}" name="Table2" displayName="Table2" ref="S33:T37" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <autoFilter ref="S33:T37" xr:uid="{59722358-51FC-47C5-BE58-6079BEEAA5D7}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{106C2011-3EF6-4B2A-81EE-A1C34F5A35B7}" name="number of orders by :" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{D424500C-273D-4584-9E54-AB032F3C62E6}" name="orders" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{106C2011-3EF6-4B2A-81EE-A1C34F5A35B7}" name="number of orders by :" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{D424500C-273D-4584-9E54-AB032F3C62E6}" name="orders" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -49788,7 +49816,7 @@
       <c r="X1000" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F1:F499 F501:F1048576 V47">
     <cfRule type="top10" dxfId="13" priority="7" bottom="1" rank="10"/>
     <cfRule type="top10" dxfId="12" priority="8" rank="10"/>
@@ -50674,7 +50702,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E2:F11">
     <sortCondition ref="E2:E11" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F1:F1048576">
     <cfRule type="dataBar" priority="5">
       <dataBar>
@@ -50844,76 +50872,128 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590F0D32-DBB8-4CC9-8A57-171EDF175381}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>593</v>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="34"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="34" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="34">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="34"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" s="34"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="34">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="34"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="74" t="s">
+        <v>697</v>
+      </c>
+      <c r="B21" s="74">
+        <f>COUNT(B8:B19)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="74" t="s">
+        <v>698</v>
+      </c>
+      <c r="B22" s="74">
+        <f>COUNTBLANK(B8:B19)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="74" t="s">
+        <v>699</v>
+      </c>
+      <c r="B23" s="74">
+        <f>COUNTA(B8:B19)</f>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -50989,7 +51069,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -51065,7 +51145,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -51508,7 +51588,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
